--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4620"/>
+  <dimension ref="A1:F4621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92812,19 +92812,39 @@
         <v>46276</v>
       </c>
       <c r="B4620" t="n">
-        <v>27.36</v>
+        <v>27.36000061035156</v>
       </c>
       <c r="C4620" t="n">
-        <v>27.83</v>
+        <v>27.82999992370605</v>
       </c>
       <c r="D4620" t="n">
         <v>27.25</v>
       </c>
       <c r="E4620" t="n">
-        <v>27.83</v>
+        <v>27.82999992370605</v>
       </c>
       <c r="F4620" t="n">
         <v>5936800</v>
+      </c>
+    </row>
+    <row r="4621">
+      <c r="A4621" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4621" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="C4621" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D4621" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="E4621" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="F4621" t="n">
+        <v>8129100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4621"/>
+  <dimension ref="A1:F4622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92832,19 +92832,39 @@
         <v>46279</v>
       </c>
       <c r="B4621" t="n">
-        <v>26.94</v>
+        <v>26.94000053405762</v>
       </c>
       <c r="C4621" t="n">
-        <v>27.2</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="D4621" t="n">
-        <v>26.26</v>
+        <v>26.26000022888184</v>
       </c>
       <c r="E4621" t="n">
-        <v>26.69</v>
+        <v>26.69000053405762</v>
       </c>
       <c r="F4621" t="n">
         <v>8129100</v>
+      </c>
+    </row>
+    <row r="4622">
+      <c r="A4622" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4622" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="C4622" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="D4622" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="E4622" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="F4622" t="n">
+        <v>7081100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4622"/>
+  <dimension ref="A1:F4623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92852,19 +92852,39 @@
         <v>46280</v>
       </c>
       <c r="B4622" t="n">
-        <v>26.98</v>
+        <v>26.97999954223633</v>
       </c>
       <c r="C4622" t="n">
-        <v>27.26</v>
+        <v>27.26000022888184</v>
       </c>
       <c r="D4622" t="n">
-        <v>26.83</v>
+        <v>26.82999992370605</v>
       </c>
       <c r="E4622" t="n">
-        <v>27.07</v>
+        <v>27.06999969482422</v>
       </c>
       <c r="F4622" t="n">
         <v>7081100</v>
+      </c>
+    </row>
+    <row r="4623">
+      <c r="A4623" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4623" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4623" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D4623" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="E4623" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="F4623" t="n">
+        <v>10333800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4623"/>
+  <dimension ref="A1:F4624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92875,16 +92875,36 @@
         <v>27</v>
       </c>
       <c r="C4623" t="n">
-        <v>27.2</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="D4623" t="n">
-        <v>26.62</v>
+        <v>26.6200008392334</v>
       </c>
       <c r="E4623" t="n">
-        <v>26.84</v>
+        <v>26.84000015258789</v>
       </c>
       <c r="F4623" t="n">
         <v>10333800</v>
+      </c>
+    </row>
+    <row r="4624">
+      <c r="A4624" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4624" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="C4624" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D4624" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="E4624" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="F4624" t="n">
+        <v>11139500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4624"/>
+  <dimension ref="A1:F4625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92891,20 +92891,32 @@
       <c r="A4624" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4624" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="C4624" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="D4624" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="E4624" t="n">
-        <v>27.29</v>
-      </c>
+      <c r="B4624" t="inlineStr"/>
+      <c r="C4624" t="inlineStr"/>
+      <c r="D4624" t="inlineStr"/>
+      <c r="E4624" t="inlineStr"/>
       <c r="F4624" t="n">
-        <v>11139500</v>
+        <v>13571900</v>
+      </c>
+    </row>
+    <row r="4625">
+      <c r="A4625" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4625" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="C4625" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="D4625" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="E4625" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="F4625" t="n">
+        <v>13596800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4625"/>
+  <dimension ref="A1:F4626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92891,12 +92891,20 @@
       <c r="A4624" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4624" t="inlineStr"/>
-      <c r="C4624" t="inlineStr"/>
-      <c r="D4624" t="inlineStr"/>
-      <c r="E4624" t="inlineStr"/>
+      <c r="B4624" t="n">
+        <v>27.55999946594238</v>
+      </c>
+      <c r="C4624" t="n">
+        <v>27.60000038146973</v>
+      </c>
+      <c r="D4624" t="n">
+        <v>26.51000022888184</v>
+      </c>
+      <c r="E4624" t="n">
+        <v>27.29000091552734</v>
+      </c>
       <c r="F4624" t="n">
-        <v>13571900</v>
+        <v>11139500</v>
       </c>
     </row>
     <row r="4625">
@@ -92904,19 +92912,39 @@
         <v>46283</v>
       </c>
       <c r="B4625" t="n">
-        <v>27.13</v>
+        <v>27.1299991607666</v>
       </c>
       <c r="C4625" t="n">
-        <v>27.49</v>
+        <v>27.48999977111816</v>
       </c>
       <c r="D4625" t="n">
-        <v>27.05</v>
+        <v>27.04999923706055</v>
       </c>
       <c r="E4625" t="n">
-        <v>27.28</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="F4625" t="n">
         <v>13596800</v>
+      </c>
+    </row>
+    <row r="4626">
+      <c r="A4626" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4626" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="C4626" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="D4626" t="n">
+        <v>27.38</v>
+      </c>
+      <c r="E4626" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F4626" t="n">
+        <v>11721100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4626"/>
+  <dimension ref="A1:F4627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92932,19 +92932,39 @@
         <v>46286</v>
       </c>
       <c r="B4626" t="n">
-        <v>27.97</v>
+        <v>27.96999931335449</v>
       </c>
       <c r="C4626" t="n">
-        <v>28.15</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="D4626" t="n">
-        <v>27.38</v>
+        <v>27.3799991607666</v>
       </c>
       <c r="E4626" t="n">
         <v>27.5</v>
       </c>
       <c r="F4626" t="n">
         <v>11721100</v>
+      </c>
+    </row>
+    <row r="4627">
+      <c r="A4627" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4627" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C4627" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="D4627" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="E4627" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="F4627" t="n">
+        <v>17157100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4627"/>
+  <dimension ref="A1:F4628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92952,19 +92952,39 @@
         <v>46287</v>
       </c>
       <c r="B4627" t="n">
-        <v>27.7</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="C4627" t="n">
-        <v>28.01</v>
+        <v>28.01000022888184</v>
       </c>
       <c r="D4627" t="n">
-        <v>27.39</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="E4627" t="n">
-        <v>27.55</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="F4627" t="n">
         <v>17157100</v>
+      </c>
+    </row>
+    <row r="4628">
+      <c r="A4628" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4628" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="C4628" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D4628" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="E4628" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="F4628" t="n">
+        <v>6301700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4628"/>
+  <dimension ref="A1:F4629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92972,19 +92972,39 @@
         <v>46288</v>
       </c>
       <c r="B4628" t="n">
-        <v>27.78</v>
+        <v>27.78000068664551</v>
       </c>
       <c r="C4628" t="n">
-        <v>27.93</v>
+        <v>27.93000030517578</v>
       </c>
       <c r="D4628" t="n">
-        <v>27.28</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="E4628" t="n">
-        <v>27.34</v>
+        <v>27.34000015258789</v>
       </c>
       <c r="F4628" t="n">
         <v>6301700</v>
+      </c>
+    </row>
+    <row r="4629">
+      <c r="A4629" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4629" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C4629" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="D4629" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="E4629" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="F4629" t="n">
+        <v>7049900</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4629"/>
+  <dimension ref="A1:F4630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92992,19 +92992,39 @@
         <v>46289</v>
       </c>
       <c r="B4629" t="n">
-        <v>27.2</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="C4629" t="n">
-        <v>27.92</v>
+        <v>27.92000007629395</v>
       </c>
       <c r="D4629" t="n">
-        <v>27.12</v>
+        <v>27.1200008392334</v>
       </c>
       <c r="E4629" t="n">
-        <v>27.92</v>
+        <v>27.92000007629395</v>
       </c>
       <c r="F4629" t="n">
         <v>7049900</v>
+      </c>
+    </row>
+    <row r="4630">
+      <c r="A4630" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4630" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C4630" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D4630" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="E4630" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="F4630" t="n">
+        <v>5247300</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4630"/>
+  <dimension ref="A1:F4631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93012,19 +93012,39 @@
         <v>46290</v>
       </c>
       <c r="B4630" t="n">
-        <v>27.4</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="C4630" t="n">
-        <v>27.6</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="D4630" t="n">
-        <v>27.01</v>
+        <v>27.01000022888184</v>
       </c>
       <c r="E4630" t="n">
-        <v>27.15</v>
+        <v>27.14999961853027</v>
       </c>
       <c r="F4630" t="n">
         <v>5247300</v>
+      </c>
+    </row>
+    <row r="4631">
+      <c r="A4631" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4631" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="C4631" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="D4631" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="E4631" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="F4631" t="n">
+        <v>6896400</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4631"/>
+  <dimension ref="A1:F4632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93035,16 +93035,36 @@
         <v>26.75</v>
       </c>
       <c r="C4631" t="n">
-        <v>27.17</v>
+        <v>27.17000007629395</v>
       </c>
       <c r="D4631" t="n">
-        <v>26.54</v>
+        <v>26.54000091552734</v>
       </c>
       <c r="E4631" t="n">
-        <v>27.02</v>
+        <v>27.02000045776367</v>
       </c>
       <c r="F4631" t="n">
         <v>6896400</v>
+      </c>
+    </row>
+    <row r="4632">
+      <c r="A4632" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4632" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C4632" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="D4632" t="n">
+        <v>26.58</v>
+      </c>
+      <c r="E4632" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F4632" t="n">
+        <v>5205200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4632"/>
+  <dimension ref="A1:F4633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93052,19 +93052,39 @@
         <v>46294</v>
       </c>
       <c r="B4632" t="n">
-        <v>27.1</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="C4632" t="n">
-        <v>27.21</v>
+        <v>27.20000076293945</v>
       </c>
       <c r="D4632" t="n">
-        <v>26.58</v>
+        <v>26.57999992370605</v>
       </c>
       <c r="E4632" t="n">
         <v>26.75</v>
       </c>
       <c r="F4632" t="n">
-        <v>5205200</v>
+        <v>5208100</v>
+      </c>
+    </row>
+    <row r="4633">
+      <c r="A4633" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4633" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="C4633" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="D4633" t="n">
+        <v>27.18</v>
+      </c>
+      <c r="E4633" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="F4633" t="n">
+        <v>12377600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4633"/>
+  <dimension ref="A1:F4634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93072,19 +93072,39 @@
         <v>46295</v>
       </c>
       <c r="B4633" t="n">
-        <v>27.87</v>
+        <v>27.8700008392334</v>
       </c>
       <c r="C4633" t="n">
-        <v>28.07</v>
+        <v>28.06999969482422</v>
       </c>
       <c r="D4633" t="n">
-        <v>27.18</v>
+        <v>27.19000053405762</v>
       </c>
       <c r="E4633" t="n">
-        <v>27.94</v>
+        <v>27.94000053405762</v>
       </c>
       <c r="F4633" t="n">
         <v>12377600</v>
+      </c>
+    </row>
+    <row r="4634">
+      <c r="A4634" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4634" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="C4634" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="D4634" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="E4634" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="F4634" t="n">
+        <v>8503800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4634"/>
+  <dimension ref="A1:F4635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93092,19 +93092,39 @@
         <v>46296</v>
       </c>
       <c r="B4634" t="n">
-        <v>28.04</v>
+        <v>28.1299991607666</v>
       </c>
       <c r="C4634" t="n">
-        <v>28.29</v>
+        <v>28.29000091552734</v>
       </c>
       <c r="D4634" t="n">
-        <v>27.47</v>
+        <v>27.46999931335449</v>
       </c>
       <c r="E4634" t="n">
-        <v>28.15</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="F4634" t="n">
         <v>8503800</v>
+      </c>
+    </row>
+    <row r="4635">
+      <c r="A4635" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4635" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="C4635" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="D4635" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="E4635" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="F4635" t="n">
+        <v>10561300</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4635"/>
+  <dimension ref="A1:F4636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93112,19 +93112,39 @@
         <v>46297</v>
       </c>
       <c r="B4635" t="n">
-        <v>28.71</v>
+        <v>28.70999908447266</v>
       </c>
       <c r="C4635" t="n">
-        <v>28.89</v>
+        <v>28.88999938964844</v>
       </c>
       <c r="D4635" t="n">
-        <v>27.86</v>
+        <v>27.86000061035156</v>
       </c>
       <c r="E4635" t="n">
-        <v>28.89</v>
+        <v>28.88999938964844</v>
       </c>
       <c r="F4635" t="n">
         <v>10561300</v>
+      </c>
+    </row>
+    <row r="4636">
+      <c r="A4636" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B4636" t="n">
+        <v>30.26</v>
+      </c>
+      <c r="C4636" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="D4636" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="E4636" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="F4636" t="n">
+        <v>30370800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4636"/>
+  <dimension ref="A1:F4637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93132,19 +93132,39 @@
         <v>46300</v>
       </c>
       <c r="B4636" t="n">
-        <v>30.26</v>
+        <v>30.26000022888184</v>
       </c>
       <c r="C4636" t="n">
-        <v>31.69</v>
+        <v>31.67000007629395</v>
       </c>
       <c r="D4636" t="n">
-        <v>29.97</v>
+        <v>29.96999931335449</v>
       </c>
       <c r="E4636" t="n">
-        <v>30.23</v>
+        <v>30.22999954223633</v>
       </c>
       <c r="F4636" t="n">
         <v>30370800</v>
+      </c>
+    </row>
+    <row r="4637">
+      <c r="A4637" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B4637" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="C4637" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="D4637" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="E4637" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="F4637" t="n">
+        <v>15702800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4637"/>
+  <dimension ref="A1:F4638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93152,19 +93152,39 @@
         <v>46301</v>
       </c>
       <c r="B4637" t="n">
-        <v>30.24</v>
+        <v>30.23999977111816</v>
       </c>
       <c r="C4637" t="n">
-        <v>30.95</v>
+        <v>30.95000076293945</v>
       </c>
       <c r="D4637" t="n">
-        <v>29.77</v>
+        <v>29.77000045776367</v>
       </c>
       <c r="E4637" t="n">
-        <v>30.63</v>
+        <v>30.6299991607666</v>
       </c>
       <c r="F4637" t="n">
         <v>15702800</v>
+      </c>
+    </row>
+    <row r="4638">
+      <c r="A4638" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4638" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="C4638" t="n">
+        <v>30.61</v>
+      </c>
+      <c r="D4638" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="E4638" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="F4638" t="n">
+        <v>22997100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4638"/>
+  <dimension ref="A1:F4639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93172,19 +93172,39 @@
         <v>46302</v>
       </c>
       <c r="B4638" t="n">
-        <v>30.4</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="C4638" t="n">
-        <v>30.61</v>
+        <v>30.61000061035156</v>
       </c>
       <c r="D4638" t="n">
-        <v>29.97</v>
+        <v>29.97999954223633</v>
       </c>
       <c r="E4638" t="n">
-        <v>30.35</v>
+        <v>30.35000038146973</v>
       </c>
       <c r="F4638" t="n">
         <v>22997100</v>
+      </c>
+    </row>
+    <row r="4639">
+      <c r="A4639" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4639" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="C4639" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="D4639" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="E4639" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="F4639" t="n">
+        <v>26693400</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4639"/>
+  <dimension ref="A1:F4640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93192,19 +93192,39 @@
         <v>46303</v>
       </c>
       <c r="B4639" t="n">
-        <v>30.81</v>
+        <v>30.80999946594238</v>
       </c>
       <c r="C4639" t="n">
-        <v>31.27</v>
+        <v>31.27000045776367</v>
       </c>
       <c r="D4639" t="n">
-        <v>30.27</v>
+        <v>30.27000045776367</v>
       </c>
       <c r="E4639" t="n">
-        <v>30.39</v>
+        <v>30.38999938964844</v>
       </c>
       <c r="F4639" t="n">
         <v>26693400</v>
+      </c>
+    </row>
+    <row r="4640">
+      <c r="A4640" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4640" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="C4640" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="D4640" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E4640" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="F4640" t="n">
+        <v>15970500</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -93212,16 +93212,16 @@
         <v>46304</v>
       </c>
       <c r="B4640" t="n">
-        <v>31.41</v>
+        <v>31.40999984741211</v>
       </c>
       <c r="C4640" t="n">
-        <v>31.66</v>
+        <v>31.65999984741211</v>
       </c>
       <c r="D4640" t="n">
-        <v>30.9</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="E4640" t="n">
-        <v>31.03</v>
+        <v>31.03000068664551</v>
       </c>
       <c r="F4640" t="n">
         <v>15970500</v>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4640"/>
+  <dimension ref="A1:F4641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93227,6 +93227,26 @@
         <v>15970500</v>
       </c>
     </row>
+    <row r="4641">
+      <c r="A4641" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4641" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="C4641" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="D4641" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="E4641" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="F4641" t="n">
+        <v>10195500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4641"/>
+  <dimension ref="A1:F4642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93232,19 +93232,39 @@
         <v>46308</v>
       </c>
       <c r="B4641" t="n">
-        <v>31.35</v>
+        <v>31.35000038146973</v>
       </c>
       <c r="C4641" t="n">
-        <v>31.58</v>
+        <v>31.55999946594238</v>
       </c>
       <c r="D4641" t="n">
-        <v>30.87</v>
+        <v>30.8700008392334</v>
       </c>
       <c r="E4641" t="n">
-        <v>31.32</v>
+        <v>31.31999969482422</v>
       </c>
       <c r="F4641" t="n">
         <v>10195500</v>
+      </c>
+    </row>
+    <row r="4642">
+      <c r="A4642" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4642" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="C4642" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D4642" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="E4642" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="F4642" t="n">
+        <v>17366000</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4642"/>
+  <dimension ref="A1:F4643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93252,19 +93252,39 @@
         <v>46309</v>
       </c>
       <c r="B4642" t="n">
-        <v>31.68</v>
+        <v>31.68000030517578</v>
       </c>
       <c r="C4642" t="n">
-        <v>31.9</v>
+        <v>31.8799991607666</v>
       </c>
       <c r="D4642" t="n">
-        <v>30.79</v>
+        <v>30.79000091552734</v>
       </c>
       <c r="E4642" t="n">
-        <v>31.08</v>
+        <v>31.07999992370605</v>
       </c>
       <c r="F4642" t="n">
         <v>17366000</v>
+      </c>
+    </row>
+    <row r="4643">
+      <c r="A4643" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4643" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="C4643" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="D4643" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="E4643" t="n">
+        <v>31.08</v>
+      </c>
+      <c r="F4643" t="n">
+        <v>11454600</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4643"/>
+  <dimension ref="A1:F4644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93272,19 +93272,39 @@
         <v>46310</v>
       </c>
       <c r="B4643" t="n">
-        <v>31.42</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="C4643" t="n">
-        <v>32.02</v>
+        <v>32.02000045776367</v>
       </c>
       <c r="D4643" t="n">
-        <v>31.04</v>
+        <v>31.04000091552734</v>
       </c>
       <c r="E4643" t="n">
-        <v>31.08</v>
+        <v>31.07999992370605</v>
       </c>
       <c r="F4643" t="n">
         <v>11454600</v>
+      </c>
+    </row>
+    <row r="4644">
+      <c r="A4644" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4644" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C4644" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="D4644" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="E4644" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="F4644" t="n">
+        <v>15592100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4644"/>
+  <dimension ref="A1:F4645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93295,16 +93295,36 @@
         <v>31.5</v>
       </c>
       <c r="C4644" t="n">
+        <v>31.89999961853027</v>
+      </c>
+      <c r="D4644" t="n">
+        <v>31.21999931335449</v>
+      </c>
+      <c r="E4644" t="n">
+        <v>31.54000091552734</v>
+      </c>
+      <c r="F4644" t="n">
+        <v>15584400</v>
+      </c>
+    </row>
+    <row r="4645">
+      <c r="A4645" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4645" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="C4645" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="D4645" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="E4645" t="n">
         <v>31.9</v>
       </c>
-      <c r="D4644" t="n">
-        <v>31.22</v>
-      </c>
-      <c r="E4644" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="F4644" t="n">
-        <v>15592100</v>
+      <c r="F4645" t="n">
+        <v>8670100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4645"/>
+  <dimension ref="A1:F4646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93312,19 +93312,39 @@
         <v>46314</v>
       </c>
       <c r="B4645" t="n">
-        <v>31.4</v>
+        <v>31.39999961853027</v>
       </c>
       <c r="C4645" t="n">
-        <v>32.09</v>
+        <v>32.09000015258789</v>
       </c>
       <c r="D4645" t="n">
-        <v>31.29</v>
+        <v>31.29000091552734</v>
       </c>
       <c r="E4645" t="n">
-        <v>31.9</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="F4645" t="n">
         <v>8670100</v>
+      </c>
+    </row>
+    <row r="4646">
+      <c r="A4646" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4646" t="n">
+        <v>32</v>
+      </c>
+      <c r="C4646" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="D4646" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E4646" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="F4646" t="n">
+        <v>12311100</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4646"/>
+  <dimension ref="A1:F4647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93335,16 +93335,36 @@
         <v>32</v>
       </c>
       <c r="C4646" t="n">
-        <v>32.42</v>
+        <v>32.40000152587891</v>
       </c>
       <c r="D4646" t="n">
-        <v>31.8</v>
+        <v>31.79999923706055</v>
       </c>
       <c r="E4646" t="n">
-        <v>31.99</v>
+        <v>31.98999977111816</v>
       </c>
       <c r="F4646" t="n">
         <v>12311100</v>
+      </c>
+    </row>
+    <row r="4647">
+      <c r="A4647" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4647" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="C4647" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="D4647" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="E4647" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="F4647" t="n">
+        <v>9480900</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4647"/>
+  <dimension ref="A1:F4648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93352,19 +93352,39 @@
         <v>46316</v>
       </c>
       <c r="B4647" t="n">
-        <v>32.17</v>
+        <v>32.16999816894531</v>
       </c>
       <c r="C4647" t="n">
-        <v>32.39</v>
+        <v>32.38999938964844</v>
       </c>
       <c r="D4647" t="n">
-        <v>31.49</v>
+        <v>31.5</v>
       </c>
       <c r="E4647" t="n">
-        <v>32.15</v>
+        <v>32.15000152587891</v>
       </c>
       <c r="F4647" t="n">
         <v>9480900</v>
+      </c>
+    </row>
+    <row r="4648">
+      <c r="A4648" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4648" t="n">
+        <v>32</v>
+      </c>
+      <c r="C4648" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="D4648" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="E4648" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="F4648" t="n">
+        <v>13839800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4648"/>
+  <dimension ref="A1:F4649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93375,16 +93375,36 @@
         <v>32</v>
       </c>
       <c r="C4648" t="n">
-        <v>32.33</v>
+        <v>32.33000183105469</v>
       </c>
       <c r="D4648" t="n">
-        <v>31.59</v>
+        <v>31.59000015258789</v>
       </c>
       <c r="E4648" t="n">
-        <v>32.14</v>
+        <v>32.13999938964844</v>
       </c>
       <c r="F4648" t="n">
         <v>13839800</v>
+      </c>
+    </row>
+    <row r="4649">
+      <c r="A4649" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4649" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="C4649" t="n">
+        <v>32.11</v>
+      </c>
+      <c r="D4649" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="E4649" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="F4649" t="n">
+        <v>13202300</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4649"/>
+  <dimension ref="A1:F4650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93392,19 +93392,39 @@
         <v>46318</v>
       </c>
       <c r="B4649" t="n">
-        <v>31.48</v>
+        <v>31.47999954223633</v>
       </c>
       <c r="C4649" t="n">
-        <v>32.11</v>
+        <v>32.11000061035156</v>
       </c>
       <c r="D4649" t="n">
-        <v>31.36</v>
+        <v>31.36000061035156</v>
       </c>
       <c r="E4649" t="n">
-        <v>31.85</v>
+        <v>31.85000038146973</v>
       </c>
       <c r="F4649" t="n">
         <v>13202300</v>
+      </c>
+    </row>
+    <row r="4650">
+      <c r="A4650" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4650" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="C4650" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D4650" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4650" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="F4650" t="n">
+        <v>40344800</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4650"/>
+  <dimension ref="A1:F4651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93412,19 +93412,39 @@
         <v>46321</v>
       </c>
       <c r="B4650" t="n">
-        <v>26.67</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="C4650" t="n">
         <v>27.5</v>
       </c>
       <c r="D4650" t="n">
-        <v>23</v>
+        <v>24.55999946594238</v>
       </c>
       <c r="E4650" t="n">
-        <v>26.99</v>
+        <v>26.98999977111816</v>
       </c>
       <c r="F4650" t="n">
         <v>40344800</v>
+      </c>
+    </row>
+    <row r="4651">
+      <c r="A4651" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4651" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="C4651" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="D4651" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E4651" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="F4651" t="n">
+        <v>20809200</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4651"/>
+  <dimension ref="A1:F4652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93432,19 +93432,39 @@
         <v>46322</v>
       </c>
       <c r="B4651" t="n">
-        <v>26.93</v>
+        <v>26.93000030517578</v>
       </c>
       <c r="C4651" t="n">
-        <v>27.35</v>
+        <v>27.35000038146973</v>
       </c>
       <c r="D4651" t="n">
-        <v>26.3</v>
+        <v>26.31999969482422</v>
       </c>
       <c r="E4651" t="n">
-        <v>26.72</v>
+        <v>26.71999931335449</v>
       </c>
       <c r="F4651" t="n">
         <v>20809200</v>
+      </c>
+    </row>
+    <row r="4652">
+      <c r="A4652" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4652" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="C4652" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="D4652" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="E4652" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F4652" t="n">
+        <v>18183700</v>
       </c>
     </row>
   </sheetData>

--- a/database/ENEV3.xlsx
+++ b/database/ENEV3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4652"/>
+  <dimension ref="A1:F4653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93452,19 +93452,39 @@
         <v>46323</v>
       </c>
       <c r="B4652" t="n">
-        <v>26.38</v>
+        <v>26.3799991607666</v>
       </c>
       <c r="C4652" t="n">
-        <v>27.08</v>
+        <v>27.07999992370605</v>
       </c>
       <c r="D4652" t="n">
-        <v>26.06</v>
+        <v>26.05999946594238</v>
       </c>
       <c r="E4652" t="n">
-        <v>26.65</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="F4652" t="n">
         <v>18183700</v>
+      </c>
+    </row>
+    <row r="4653">
+      <c r="A4653" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4653" t="n">
+        <v>25.83</v>
+      </c>
+      <c r="C4653" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="D4653" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="E4653" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="F4653" t="n">
+        <v>13412100</v>
       </c>
     </row>
   </sheetData>
